--- a/labo/FPGA_MSXtR_CPU_Stack_001_RENEW/src/cz80/SlotTiming.xlsx
+++ b/labo/FPGA_MSXtR_CPU_Stack_001_RENEW/src/cz80/SlotTiming.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hra\Documents\github\HRA_product\FPGA_MSXtR\labo\FPGA_MSXtR_CPU_Stack_001_RENEW\src\cz80\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3F1131-DB28-4E6C-A590-5A96B7BA12BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAB2072-02DF-4AC8-8748-21D8D3328AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4170" windowWidth="25065" windowHeight="13110" activeTab="1" xr2:uid="{AC65AD65-EC2C-4009-86B9-C5FE140E570A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{AC65AD65-EC2C-4009-86B9-C5FE140E570A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2004,13 +2004,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98D36E6F-7649-45C1-8194-863B431B5DB5}">
-  <dimension ref="B2:L41"/>
+  <dimension ref="B2:J41"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="7" max="8" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B2">
         <v>42.954540000000001</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B3">
         <v>3.579545</v>
       </c>
@@ -2037,12 +2037,8 @@
       <c r="E3" t="s">
         <v>28</v>
       </c>
-      <c r="L3">
-        <f>D3*2.5</f>
-        <v>698.41278710003644</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.4">
       <c r="F5" t="s">
         <v>29</v>
       </c>
@@ -2056,7 +2052,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.4">
       <c r="F6" t="s">
         <v>31</v>
       </c>
@@ -2070,12 +2066,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.4">
       <c r="E8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.4">
       <c r="F9" t="s">
         <v>33</v>
       </c>
@@ -2089,7 +2085,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.4">
       <c r="F10" t="s">
         <v>35</v>
       </c>
@@ -2103,7 +2099,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.4">
       <c r="F11" t="s">
         <v>37</v>
       </c>
@@ -2117,7 +2113,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.4">
       <c r="F12" t="s">
         <v>38</v>
       </c>
@@ -2131,7 +2127,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.4">
       <c r="F13" t="s">
         <v>39</v>
       </c>
@@ -2148,7 +2144,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.4">
       <c r="F14" t="s">
         <v>41</v>
       </c>
@@ -2165,7 +2161,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.4">
       <c r="F15" t="s">
         <v>42</v>
       </c>
@@ -2182,7 +2178,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.4">
       <c r="F16" t="s">
         <v>43</v>
       </c>
